--- a/data/curriculo_unicafam/mig_propuestas/PROP_04_Maestr_a_en_Inteligencia__MIG.xlsx
+++ b/data/curriculo_unicafam/mig_propuestas/PROP_04_Maestr_a_en_Inteligencia__MIG.xlsx
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -182,6 +182,22 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -548,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:H46"/>
+  <dimension ref="B1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -643,7 +659,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>MAESTRÍA EN INTELIGENCIA ARTIFICIAL Y ANALÍTICA ESTRATÉGICA</t>
+          <t>MAESTRÍA EN INTELIGENCIA ARTIFICIAL Y CIENCIA DE DATOS ESTRATÉGICA</t>
         </is>
       </c>
       <c r="D6" s="2" t="n"/>
@@ -660,7 +676,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Maestría Aplicada (Posgrado) - Magíster en IA Aplicada</t>
+          <t>Maestría Aplicada (Posgrado / Maestría) - Magíster en Inteligencia Artificial y Ciencia de Datos Estratégica</t>
         </is>
       </c>
       <c r="D7" s="2" t="n"/>
@@ -677,7 +693,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Sábados de 8:00 a.m. a 1:00 p.m. / Sesiones sincrónicas</t>
+          <t>Jornada Nocturna y Concentrada en Fines de Semana (Híbrida)</t>
         </is>
       </c>
       <c r="D8" s="2" t="n"/>
@@ -711,7 +727,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Próximo inicio de cohorte académica</t>
+          <t>Agosto de 2025</t>
         </is>
       </c>
       <c r="D10" s="2" t="n"/>
@@ -728,7 +744,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Al completar el número total de horas del programa</t>
+          <t>Junio de 2027</t>
         </is>
       </c>
       <c r="D11" s="2" t="n"/>
@@ -750,7 +766,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Por definir según tarifario institucional</t>
+          <t>$12.500.000 COP por semestre</t>
         </is>
       </c>
       <c r="E12" s="2" t="n"/>
@@ -767,7 +783,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Descuento especial comunidad UniCafam / Afiliados Cafam</t>
+          <t>$10.000.000 COP por semestre (20% dcto egresados/docentes)</t>
         </is>
       </c>
       <c r="E13" s="2" t="n"/>
@@ -784,7 +800,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Tarifa preferencial egresados UniCafam</t>
+          <t>$10.000.000 COP por semestre (20% dcto)</t>
         </is>
       </c>
       <c r="E14" s="2" t="n"/>
@@ -801,7 +817,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Tarifa corporativa por volumen (&gt;3 inscritos)</t>
+          <t>$10.625.000 COP por semestre (15% dcto corporativo)</t>
         </is>
       </c>
       <c r="E15" s="2" t="n"/>
@@ -817,7 +833,7 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Cohortes semestrales continuas</t>
+          <t>Apertura anual para cada segundo semestre académico</t>
         </is>
       </c>
       <c r="D16" s="2" t="n"/>
@@ -835,7 +851,7 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>El presente programa responde a las demandas urgentes del mercado laboral identificadas por el Observatorio de Inteligencia Laboral de UniCafam. El análisis de vacantes revela una brecha del sector productivo en competencias de Maestría en Inteligencia Artificial y Analítica Estratégica. El impacto salarial proyectado (Acceso al mercado remoto internacional con promedios &gt; $30M COP.) sustenta la pertinencia de formar talento especializado con alta tasa de empleabilidad y proyección nacional e internacional.</t>
+          <t>La cúspide del mercado laboral analítico global está dominada por vacantes de Científicos de Datos y Machine Learning Engineers (conjuntamente representan el 78.1% de la demanda en el observatorio). Mientras las ofertas de entrada locales pagan sumas intermedias, las posiciones de dirección técnica y diseño de arquitecturas complejas de Inteligencia Artificial superan con creces los salarios promedio remotos de $32M COP, con techos salariales de hasta $68M COP. Esta maestría aplicada de UniCafam cubre el espacio estratégico de liderazgo técnico e investigación corporativa. Ofrece una continuación natural a los egresados del Profesional en Ciencia de Datos, permitiéndoles profundizar en Deep Learning avanzado (PyTorch/TensorFlow), toma de decisiones estratégicas bajo enfoques causales y gobernanza ética de IA. UniCafam se consolidará como el hub de formación avanzada del más alto nivel, articulando la academia con el mercado remoto internacional de máxima remuneración.</t>
         </is>
       </c>
       <c r="D18" s="2" t="n"/>
@@ -879,9 +895,10 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>• Desarrollar competencias especializadas en Maestría en Inteligencia Artificial y Analítica Estratégica para responder a los desafíos tecnológicos del mercado.
-• Implementar soluciones técnicas reales mediante proyectos aplicados utilizando herramientas líderes de la industria.
-• Integrar metodologías ágiles y estándares internacionales en el ciclo de vida de los datos e inteligencia artificial.</t>
+          <t>• Objetivo General: Formar líderes y tomadores de decisiones estratégicas que posean el más alto dominio tecnológico para diseñar, auditar e implementar soluciones complejas basadas en Inteligencia Artificial que generen valor económico exponencial y resuelvan problemas estructurales de las industrias.
+• Objetivo Específico 1: Diseñar arquitecturas de aprendizaje profundo complejas optimizadas para procesamiento de imagen, voz, secuencias temporales y agentes autónomos utilizando librerías avanzadas.
+• Objetivo Específico 2: Implementar enfoques de inferencia causal y modelado analítico avanzado para estructurar políticas de negocio basadas en atribución científica rigurosa.
+• Objetivo Específico 3: Establecer marcos éticos de gobernanza de la IA asegurando la privacidad, transparencia y explicabilidad algorítmica corporativa.</t>
         </is>
       </c>
       <c r="D22" s="2" t="n"/>
@@ -925,7 +942,7 @@
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Profesionales con sólida base matemática, estadística y de programación.</t>
+          <t>Profesionales y directores con perfiles en Ciencia de Datos, Ingeniería de Sistemas, Estadística, Matemáticas o profesionales con experiencia en analítica cuantitativa que deseen liderar la transformación mediante inteligencia artificial y acceder a roles directivos globales.</t>
         </is>
       </c>
       <c r="D26" s="2" t="n"/>
@@ -960,7 +977,7 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Metodología 100% teórico-práctica con enfoque en Aprendizaje Basado en Retos y Proyectos Reales (PBL). Las sesiones combinan fundamentación conceptual, laboratorios guiados en la nube y trabajo autónomo con acompañamiento de expertos de la industria. Cada módulo concluye con un entregable técnico aplicable.</t>
+          <t>Seminarios avanzados de investigación aplicada combinados con laboratorios computacionales de alto rendimiento (GPU clusters). Los estudiantes formularán un Proyecto de Grado de Aplicación Industrial que debe resolver de manera efectiva un problema analítico de alta complejidad técnica y viabilidad de mercado dentro de una empresa real. La maestría promueve activamente el desarrollo de publicaciones científicas y patentes de algoritmos.</t>
         </is>
       </c>
       <c r="D29" s="2" t="n"/>
@@ -1004,10 +1021,9 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>✔ Alineación directa con los requisitos reales de vacantes analizadas en el Observatorio Laboral.
-✔ Enfoque en tecnologías de alta prima salarial (Acceso al mercado remoto internacional con promedios &gt; $30M COP.).
-✔ Certificación institucional respaldada por la Fundación Universitaria Cafam.
-✔ Docentes activos y líderes técnicos en empresas multinacionales de tecnología.</t>
+          <t>✔ Uso de clústeres de supercómputo equipados con GPUs NVIDIA corporativas de alto rendimiento para el entrenamiento de modelos de Deep Learning complejos.
+✔ Networking corporativo de alto nivel: interacción continua con presidentes de empresas, gerentes de analítica e investigadores de todo el continente.
+✔ Homologación automática de créditos para egresados de la Especialización de UniCafam, reduciendo drásticamente la inversión y el tiempo de estudio de la maestría.</t>
         </is>
       </c>
       <c r="D33" s="2" t="n"/>
@@ -1100,28 +1116,28 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Deep Learning y Procesamiento de Lenguaje Natural (NLP/LLMs)</t>
+          <t>Modelado Avanzado de Aprendizaje Profundo &amp; Redes Neuronales</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>Unidades Temáticas:
-1. Fundamentación y Arquitectura.
-2. Implementación Práctica y Laboratorios (PyTorch, Hugging Face, LangChain, TensorFlow).
-3. Proyecto de Aplicación y Evaluación.
-Resultados de Aprendizaje:
-Desarrollar aplicaciones basadas en modelos de lenguaje de gran escala y arquitecturas de redes neuronales profundas. [Stack: PyTorch, Hugging Face, LangChain, TensorFlow]</t>
+          <t>1. Introducción al entrenamiento por retropropagación y gradientes en redes profundas.
+2. Arquitecturas de visión artificial complejas (CNNs y Redes Generativas Adversarias - GANs).
+3. Redes recurrentes y procesamiento secuencial (LSTMs y GRUs).
+4. Mecanismos de atención y Transformers profundos.
+5. Modelos fundacionales e inferencia multimodal (Visión-Lenguaje).
+6. Entrenamiento eficiente de redes a escala y ajuste fino (Fine-Tuning) utilizando PyTorch. [Stack: PyTorch, TensorFlow, Keras, Hugging Face, Weights &amp; Biases]</t>
         </is>
       </c>
       <c r="F39" s="2" t="n"/>
       <c r="G39" s="15" t="inlineStr">
         <is>
-          <t>Módulo 1 - Semanas 1 a 4</t>
+          <t>Semanas 1 a 12 (Primer Semestre)</t>
         </is>
       </c>
       <c r="H39" s="16" t="inlineStr">
         <is>
-          <t>144 h</t>
+          <t>192 h</t>
         </is>
       </c>
     </row>
@@ -1143,63 +1159,88 @@
       <c r="G41" s="2" t="n"/>
       <c r="H41" s="2" t="n"/>
     </row>
-    <row r="42" ht="10" customHeight="1"/>
-    <row r="43" ht="20" customHeight="1">
-      <c r="B43" s="11" t="inlineStr">
-        <is>
-          <t>DOCENTES</t>
-        </is>
-      </c>
-      <c r="C43" s="12" t="inlineStr">
-        <is>
-          <t>Nombre del Docente / Rol</t>
-        </is>
-      </c>
-      <c r="D43" s="13" t="n"/>
-      <c r="E43" s="12" t="inlineStr">
-        <is>
-          <t>Módulo Asignado</t>
-        </is>
-      </c>
-      <c r="F43" s="12" t="inlineStr">
-        <is>
-          <t>Perfil de Experto / Requisitos y Credenciales</t>
-        </is>
-      </c>
-      <c r="G43" s="13" t="n"/>
-      <c r="H43" s="13" t="n"/>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="B44" s="13" t="n"/>
-      <c r="C44" s="13" t="n"/>
-      <c r="D44" s="13" t="n"/>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="13" t="n"/>
-      <c r="G44" s="13" t="n"/>
-      <c r="H44" s="13" t="n"/>
-    </row>
-    <row r="45" ht="24" customHeight="1">
+    <row r="42" ht="22" customHeight="1">
+      <c r="B42" s="17" t="inlineStr"/>
+      <c r="C42" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>Inferencia Causal &amp; Modelamiento Decisional para Negocios</t>
+        </is>
+      </c>
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t>1. Limitaciones de la correlación de datos convencional frente a la causalidad de eventos.
+2. Teoría de Grafos Causal y el Cálculo Do (Pearl's Causal Framework).
+3. Métodos experimentales modernos y pruebas A/B de escala industrial.
+4. Métodos cuasi-experimentales en ciencias de datos (Diff-in-Diff, RDD, Propensity Score Matching).
+5. Modelado causal para atribución comercial y optimización de políticas de precios dinámicos.
+6. Herramientas de estimación de efectos causales con Python. [Stack: DoWhy, CausalML, EconML, Statsmodels]</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="n"/>
+      <c r="G42" s="20" t="inlineStr">
+        <is>
+          <t>Semanas 1 a 12 (Segundo Semestre)</t>
+        </is>
+      </c>
+      <c r="H42" s="21" t="inlineStr">
+        <is>
+          <t>192 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" s="2" t="n"/>
+      <c r="F43" s="2" t="n"/>
+      <c r="G43" s="2" t="n"/>
+      <c r="H43" s="2" t="n"/>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="n"/>
+      <c r="F44" s="2" t="n"/>
+      <c r="G44" s="2" t="n"/>
+      <c r="H44" s="2" t="n"/>
+    </row>
+    <row r="45" ht="22" customHeight="1">
       <c r="B45" s="2" t="inlineStr"/>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>Especialista / Magíster en PyTorch</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="n"/>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>Deep Learning y Procesamiento de Lenguaje Natural (NLP/LLMs)</t>
-        </is>
-      </c>
-      <c r="F45" s="10" t="inlineStr">
-        <is>
-          <t>Profesional con más de 5 años de experiencia liderando proyectos de Deep Learning y Procesamiento de Lenguaje Natural (NLP/LLMs) en el sector productivo, con certificaciones internacionales en el stack tecnológico enseñado.</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="n"/>
-      <c r="H45" s="2" t="n"/>
-    </row>
-    <row r="46" ht="24" customHeight="1">
+      <c r="C45" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>Gobernanza de Datos, Ética en IA &amp; Algoritmos Explicables (XAI)</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>1. Sesgo algorítmico, equidad informática (Algorithmic Fairness) y discriminación por IA.
+2. Métodos de interpretación y explicación de modelos complejos de caja negra (SHAP, LIME).
+3. Cumplimiento normativo e internacional de privacidad de datos (GDPR, Ley de Inteligencia Artificial de la UE y normativas locales del MEN).
+4. Gobierno de datos y aseguramiento de la robustez frente a ataques adversarios de modelos.
+5. Marcos de auditoría ética y responsabilidad corporativa algorítmica. [Stack: SHAP, LIME, Fairlearn, Alibi, InterpretML]</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="n"/>
+      <c r="G45" s="15" t="inlineStr">
+        <is>
+          <t>Semanas 1 a 12 (Tercer Semestre)</t>
+        </is>
+      </c>
+      <c r="H45" s="16" t="inlineStr">
+        <is>
+          <t>192 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
       <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="n"/>
@@ -1208,52 +1249,206 @@
       <c r="G46" s="2" t="n"/>
       <c r="H46" s="2" t="n"/>
     </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n"/>
+      <c r="E47" s="2" t="n"/>
+      <c r="F47" s="2" t="n"/>
+      <c r="G47" s="2" t="n"/>
+      <c r="H47" s="2" t="n"/>
+    </row>
+    <row r="48" ht="10" customHeight="1"/>
+    <row r="49" ht="20" customHeight="1">
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>DOCENTES</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>Nombre del Docente / Rol</t>
+        </is>
+      </c>
+      <c r="D49" s="13" t="n"/>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>Módulo Asignado</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="inlineStr">
+        <is>
+          <t>Perfil de Experto / Requisitos y Credenciales</t>
+        </is>
+      </c>
+      <c r="G49" s="13" t="n"/>
+      <c r="H49" s="13" t="n"/>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="B50" s="13" t="n"/>
+      <c r="C50" s="13" t="n"/>
+      <c r="D50" s="13" t="n"/>
+      <c r="E50" s="13" t="n"/>
+      <c r="F50" s="13" t="n"/>
+      <c r="G50" s="13" t="n"/>
+      <c r="H50" s="13" t="n"/>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Científico de Datos Senior con Doctorado en Ciencias de la Computación / Deep Learning</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n"/>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>Modelado Avanzado de Aprendizaje Profundo &amp; Redes Neuronales</t>
+        </is>
+      </c>
+      <c r="F51" s="10" t="inlineStr">
+        <is>
+          <t>Ph.D. en Computación o IA con amplias publicaciones científicas indexadas Q1 o Q2 en aprendizaje automático, con amplia experiencia de modelado complejo con frameworks de cómputo en la nube a gran escala.</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="n"/>
+      <c r="H51" s="2" t="n"/>
+    </row>
+    <row r="52" ht="24" customHeight="1">
+      <c r="B52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n"/>
+      <c r="E52" s="2" t="n"/>
+      <c r="F52" s="2" t="n"/>
+      <c r="G52" s="2" t="n"/>
+      <c r="H52" s="2" t="n"/>
+    </row>
+    <row r="53" ht="24" customHeight="1">
+      <c r="B53" s="17" t="inlineStr"/>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>Especialista en Inferencia Causal y Econometría Analítica</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n"/>
+      <c r="E53" s="22" t="inlineStr">
+        <is>
+          <t>Inferencia Causal &amp; Modelamiento Decisional para Negocios</t>
+        </is>
+      </c>
+      <c r="F53" s="19" t="inlineStr">
+        <is>
+          <t>Doctor en Economía Cuantitativa o Estadística Aplicada, con vasta trayectoria laboral en diseño de experimentos de alta precisión de comportamiento de consumo e inferencia para industrias digitales de primer nivel.</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n"/>
+      <c r="H53" s="2" t="n"/>
+    </row>
+    <row r="54" ht="24" customHeight="1">
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n"/>
+      <c r="E54" s="2" t="n"/>
+      <c r="F54" s="2" t="n"/>
+      <c r="G54" s="2" t="n"/>
+      <c r="H54" s="2" t="n"/>
+    </row>
+    <row r="55" ht="24" customHeight="1">
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Experto en Regulación de Datos y XAI (Explainable AI)</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n"/>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>Gobernanza de Datos, Ética en IA &amp; Algoritmos Explicables (XAI)</t>
+        </is>
+      </c>
+      <c r="F55" s="10" t="inlineStr">
+        <is>
+          <t>Ph.D. o Magíster en Ética Aplicada, Derecho de TI o Ciencia de Datos, que haya liderado procesos de auditoría del comportamiento ético de algoritmos de decisión de otorgamiento de crédito o contratación en entidades de la Unión Europea o América Latina.</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n"/>
+      <c r="H55" s="2" t="n"/>
+    </row>
+    <row r="56" ht="24" customHeight="1">
+      <c r="B56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n"/>
+      <c r="E56" s="2" t="n"/>
+      <c r="F56" s="2" t="n"/>
+      <c r="G56" s="2" t="n"/>
+      <c r="H56" s="2" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="45">
+  <mergeCells count="65">
     <mergeCell ref="B22:B25"/>
-    <mergeCell ref="E43:E44"/>
     <mergeCell ref="C10:H10"/>
     <mergeCell ref="C16:H16"/>
-    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="C55:D56"/>
+    <mergeCell ref="G45:G47"/>
     <mergeCell ref="C39:C41"/>
     <mergeCell ref="G2:H2"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="E51:E52"/>
     <mergeCell ref="C9:H9"/>
     <mergeCell ref="B12:B15"/>
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="C26:H28"/>
+    <mergeCell ref="E42:F44"/>
+    <mergeCell ref="F49:H50"/>
     <mergeCell ref="B33:B35"/>
-    <mergeCell ref="C43:D44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="C51:D52"/>
     <mergeCell ref="E39:F41"/>
     <mergeCell ref="C11:H11"/>
+    <mergeCell ref="B45:B47"/>
     <mergeCell ref="D39:D41"/>
     <mergeCell ref="E38:F38"/>
     <mergeCell ref="B26:B28"/>
+    <mergeCell ref="F53:H54"/>
     <mergeCell ref="C18:H21"/>
     <mergeCell ref="D13:H13"/>
     <mergeCell ref="G37:H37"/>
+    <mergeCell ref="H42:H44"/>
     <mergeCell ref="C8:H8"/>
+    <mergeCell ref="C53:D54"/>
     <mergeCell ref="B29:B32"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="C42:C44"/>
     <mergeCell ref="C7:H7"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="B1:E4"/>
     <mergeCell ref="B37:B38"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="F55:H56"/>
     <mergeCell ref="C29:H32"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C45:C47"/>
     <mergeCell ref="G39:G41"/>
-    <mergeCell ref="F45:H46"/>
+    <mergeCell ref="G42:G44"/>
     <mergeCell ref="C22:H25"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="C49:D50"/>
+    <mergeCell ref="F51:H52"/>
+    <mergeCell ref="E45:F47"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="B42:B44"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="C6:H6"/>
     <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D45:D47"/>
     <mergeCell ref="C33:H35"/>
     <mergeCell ref="D15:H15"/>
     <mergeCell ref="B39:B41"/>
     <mergeCell ref="H39:H41"/>
+    <mergeCell ref="H45:H47"/>
+    <mergeCell ref="B51:B52"/>
     <mergeCell ref="G1:H1"/>
-    <mergeCell ref="C45:D46"/>
+    <mergeCell ref="E53:E54"/>
     <mergeCell ref="E37:F37"/>
-    <mergeCell ref="F43:H44"/>
     <mergeCell ref="D14:H14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/curriculo_unicafam/mig_propuestas/PROP_04_Maestr_a_en_Inteligencia__MIG.xlsx
+++ b/data/curriculo_unicafam/mig_propuestas/PROP_04_Maestr_a_en_Inteligencia__MIG.xlsx
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -197,6 +197,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -564,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:H56"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -611,7 +614,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0 (PENDIENTE_REVISION)</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
@@ -628,7 +631,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H3" s="2" t="n"/>
@@ -1383,8 +1386,76 @@
       <c r="G56" s="2" t="n"/>
       <c r="H56" s="2" t="n"/>
     </row>
+    <row r="58" ht="24" customHeight="1">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>GOBERNANZA CURRICULAR Y TRAZABILIDAD DE APROBACIÓN (MEN DECRETO 1330)</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="n"/>
+      <c r="C58" s="13" t="n"/>
+      <c r="D58" s="13" t="n"/>
+      <c r="E58" s="13" t="n"/>
+      <c r="F58" s="13" t="n"/>
+      <c r="G58" s="13" t="n"/>
+      <c r="H58" s="13" t="n"/>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="23" t="inlineStr">
+        <is>
+          <t>ESTADO DE APROBACIÓN</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n"/>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>PENDIENTE_REVISION (Versión v1)</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n"/>
+      <c r="E59" s="2" t="n"/>
+      <c r="F59" s="2" t="n"/>
+      <c r="G59" s="2" t="n"/>
+      <c r="H59" s="2" t="n"/>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="23" t="inlineStr">
+        <is>
+          <t>AVAL / DECISIÓN DIRECTIVA</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n"/>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente de Visto Bueno por Comité Curricular</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n"/>
+      <c r="E60" s="2" t="n"/>
+      <c r="F60" s="2" t="n"/>
+      <c r="G60" s="2" t="n"/>
+      <c r="H60" s="2" t="n"/>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="23" t="inlineStr">
+        <is>
+          <t>FECHA ÚLTIMA DECISIÓN</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n"/>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>En proceso de revisión</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n"/>
+      <c r="E61" s="2" t="n"/>
+      <c r="F61" s="2" t="n"/>
+      <c r="G61" s="2" t="n"/>
+      <c r="H61" s="2" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="65">
+  <mergeCells count="72">
     <mergeCell ref="B22:B25"/>
     <mergeCell ref="C10:H10"/>
     <mergeCell ref="C16:H16"/>
@@ -1393,6 +1464,7 @@
     <mergeCell ref="C39:C41"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="E55:E56"/>
+    <mergeCell ref="A59:B59"/>
     <mergeCell ref="E51:E52"/>
     <mergeCell ref="C9:H9"/>
     <mergeCell ref="B12:B15"/>
@@ -1402,16 +1474,20 @@
     <mergeCell ref="F49:H50"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D42:D44"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="C59:H59"/>
     <mergeCell ref="C51:D52"/>
     <mergeCell ref="E39:F41"/>
     <mergeCell ref="C11:H11"/>
     <mergeCell ref="B45:B47"/>
     <mergeCell ref="D39:D41"/>
     <mergeCell ref="E38:F38"/>
+    <mergeCell ref="C60:H60"/>
     <mergeCell ref="B26:B28"/>
     <mergeCell ref="F53:H54"/>
     <mergeCell ref="C18:H21"/>
     <mergeCell ref="D13:H13"/>
+    <mergeCell ref="C61:H61"/>
     <mergeCell ref="G37:H37"/>
     <mergeCell ref="H42:H44"/>
     <mergeCell ref="C8:H8"/>
@@ -1450,6 +1526,8 @@
     <mergeCell ref="E53:E54"/>
     <mergeCell ref="E37:F37"/>
     <mergeCell ref="D14:H14"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A58:H58"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/curriculo_unicafam/mig_propuestas/PROP_04_Maestr_a_en_Inteligencia__MIG.xlsx
+++ b/data/curriculo_unicafam/mig_propuestas/PROP_04_Maestr_a_en_Inteligencia__MIG.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>1.0 (PENDIENTE_REVISION)</t>
+          <t>2.0 (PENDIENTE_REVISION)</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
@@ -631,7 +631,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H3" s="2" t="n"/>
@@ -769,7 +769,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>$12.500.000 COP por semestre</t>
+          <t>Por definir según tarifario institucional</t>
         </is>
       </c>
       <c r="E12" s="2" t="n"/>
@@ -786,7 +786,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>$10.000.000 COP por semestre (20% dcto egresados/docentes)</t>
+          <t>Por definir según tarifario institucional</t>
         </is>
       </c>
       <c r="E13" s="2" t="n"/>
@@ -803,7 +803,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>$10.000.000 COP por semestre (20% dcto)</t>
+          <t>Por definir según tarifario institucional</t>
         </is>
       </c>
       <c r="E14" s="2" t="n"/>
@@ -820,7 +820,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>$10.625.000 COP por semestre (15% dcto corporativo)</t>
+          <t>Por definir según tarifario institucional</t>
         </is>
       </c>
       <c r="E15" s="2" t="n"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>La cúspide del mercado laboral analítico global está dominada por vacantes de Científicos de Datos y Machine Learning Engineers (conjuntamente representan el 78.1% de la demanda en el observatorio). Mientras las ofertas de entrada locales pagan sumas intermedias, las posiciones de dirección técnica y diseño de arquitecturas complejas de Inteligencia Artificial superan con creces los salarios promedio remotos de $32M COP, con techos salariales de hasta $68M COP. Esta maestría aplicada de UniCafam cubre el espacio estratégico de liderazgo técnico e investigación corporativa. Ofrece una continuación natural a los egresados del Profesional en Ciencia de Datos, permitiéndoles profundizar en Deep Learning avanzado (PyTorch/TensorFlow), toma de decisiones estratégicas bajo enfoques causales y gobernanza ética de IA. UniCafam se consolidará como el hub de formación avanzada del más alto nivel, articulando la academia con el mercado remoto internacional de máxima remuneración.</t>
+          <t>Según datos del Observatorio de Empleo UniCafam (corte del 2026-10-28, n = 570 ofertas), el rol de Científico de Datos lidera la demanda en el mercado de analítica avanzada con el 31.2% de las ofertas (178 ofertas), seguido por el rol de Machine Learning / AI Engineer con el 18.2% (104 ofertas). A nivel de habilidades requeridas, Python está presente en el 56.7% de las ofertas (323 ofertas), SQL en el 62.3% (355 ofertas), ETL / Pipelines de Datos en el 45.4% (259 ofertas) y Machine Learning General en el 27.5% (157 ofertas). Habilidades especializadas como Deep Learning (4.0%, 23 ofertas), PyTorch (4.2%, 24 ofertas) y TensorFlow / Keras (4.4%, 25 ofertas) complementan las arquitecturas complejas requeridas por las organizaciones. Esta maestría aplicada aborda las brechas técnicas de alto nivel alineando el desarrollo analítico con las exigencias directivas e infraestructurales del mercado local e internacional.</t>
         </is>
       </c>
       <c r="D18" s="2" t="n"/>
@@ -898,10 +898,10 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>• Objetivo General: Formar líderes y tomadores de decisiones estratégicas que posean el más alto dominio tecnológico para diseñar, auditar e implementar soluciones complejas basadas en Inteligencia Artificial que generen valor económico exponencial y resuelvan problemas estructurales de las industrias.
-• Objetivo Específico 1: Diseñar arquitecturas de aprendizaje profundo complejas optimizadas para procesamiento de imagen, voz, secuencias temporales y agentes autónomos utilizando librerías avanzadas.
-• Objetivo Específico 2: Implementar enfoques de inferencia causal y modelado analítico avanzado para estructurar políticas de negocio basadas en atribución científica rigurosa.
-• Objetivo Específico 3: Establecer marcos éticos de gobernanza de la IA asegurando la privacidad, transparencia y explicabilidad algorítmica corporativa.</t>
+          <t>• Objetivo General: Formar magísteres con competencias de liderazgo técnico para diseñar, implementar y gestionar soluciones integrales de Inteligencia Artificial y Aprendizaje Automático orientadas a generar valor estratégico en las organizaciones.
+• Objetivo Específico 1: Diseñar arquitecturas de aprendizaje profundo utilizando Python, PyTorch y frameworks avanzados para el procesamiento de datos estructurados y no estructurados.
+• Objetivo Específico 2: Estructurar estrategias de modelamiento decisional y analítica avanzada integrando metodologías de datos para resolver problemas complejos de negocio.
+• Objetivo Específico 3: Implementar esquemas de gobernanza de datos y principios de IA explicable (XAI) asegurando el cumplimiento normativo, la transparencia y la equidad algorítmica.</t>
         </is>
       </c>
       <c r="D22" s="2" t="n"/>
@@ -945,7 +945,7 @@
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Profesionales y directores con perfiles en Ciencia de Datos, Ingeniería de Sistemas, Estadística, Matemáticas o profesionales con experiencia en analítica cuantitativa que deseen liderar la transformación mediante inteligencia artificial y acceder a roles directivos globales.</t>
+          <t>Profesionales y directores en áreas de Ciencia de Datos, Ingeniería de Sistemas, Estadística, Matemáticas o afines, con experiencia cuantitativa que busquen asumir roles de liderazgo técnico e ingeniería analítica avanzada.</t>
         </is>
       </c>
       <c r="D26" s="2" t="n"/>
@@ -980,7 +980,7 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Seminarios avanzados de investigación aplicada combinados con laboratorios computacionales de alto rendimiento (GPU clusters). Los estudiantes formularán un Proyecto de Grado de Aplicación Industrial que debe resolver de manera efectiva un problema analítico de alta complejidad técnica y viabilidad de mercado dentro de una empresa real. La maestría promueve activamente el desarrollo de publicaciones científicas y patentes de algoritmos.</t>
+          <t>Seminarios aplicados integrados con laboratorios computacionales prácticos. El programa se centra en el desarrollo de un Proyecto de Grado de Aplicación Industrial orientado a resolver problemas analíticos reales de alto impacto técnico y organizacional.</t>
         </is>
       </c>
       <c r="D29" s="2" t="n"/>
@@ -1024,9 +1024,9 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>✔ Uso de clústeres de supercómputo equipados con GPUs NVIDIA corporativas de alto rendimiento para el entrenamiento de modelos de Deep Learning complejos.
-✔ Networking corporativo de alto nivel: interacción continua con presidentes de empresas, gerentes de analítica e investigadores de todo el continente.
-✔ Homologación automática de créditos para egresados de la Especialización de UniCafam, reduciendo drásticamente la inversión y el tiempo de estudio de la maestría.</t>
+          <t>✔ Formación rigurosa alineada con las habilidades de mayor demanda del mercado: Python (56.7% de ofertas) y SQL (62.3% de ofertas) según corte 2026-10-28 (n = 570).
+✔ Integración de pipelines de datos (ETL) y marcos de gobernanza algorítmica aplicados a la toma de decisiones empresariales.
+✔ Posibilidad de articulación y homologación de créditos para egresados de posgrados de la Escuela de Ingeniería de UniCafam conforme a normativa institucional.</t>
         </is>
       </c>
       <c r="D33" s="2" t="n"/>
@@ -1124,12 +1124,11 @@
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>1. Introducción al entrenamiento por retropropagación y gradientes en redes profundas.
-2. Arquitecturas de visión artificial complejas (CNNs y Redes Generativas Adversarias - GANs).
-3. Redes recurrentes y procesamiento secuencial (LSTMs y GRUs).
-4. Mecanismos de atención y Transformers profundos.
-5. Modelos fundacionales e inferencia multimodal (Visión-Lenguaje).
-6. Entrenamiento eficiente de redes a escala y ajuste fino (Fine-Tuning) utilizando PyTorch. [Stack: PyTorch, TensorFlow, Keras, Hugging Face, Weights &amp; Biases]</t>
+          <t>1. Fundamentos de aprendizaje profundo y retropropagación.
+2. Arquitecturas convolucionales para visión por computador.
+3. Redes recurrentes y procesamiento de secuencias temporales.
+4. Mecanismos de atención y arquitecturas basadas en Transformers.
+5. Ajuste fino de modelos y optimización de cómputo en PyTorch y TensorFlow. [Stack: Python, PyTorch, TensorFlow, Keras, Hugging Face]</t>
         </is>
       </c>
       <c r="F39" s="2" t="n"/>
@@ -1174,12 +1173,11 @@
       </c>
       <c r="E42" s="19" t="inlineStr">
         <is>
-          <t>1. Limitaciones de la correlación de datos convencional frente a la causalidad de eventos.
-2. Teoría de Grafos Causal y el Cálculo Do (Pearl's Causal Framework).
-3. Métodos experimentales modernos y pruebas A/B de escala industrial.
-4. Métodos cuasi-experimentales en ciencias de datos (Diff-in-Diff, RDD, Propensity Score Matching).
-5. Modelado causal para atribución comercial y optimización de políticas de precios dinámicos.
-6. Herramientas de estimación de efectos causales con Python. [Stack: DoWhy, CausalML, EconML, Statsmodels]</t>
+          <t>1. Principios de causalidad vs. correlación en ciencia de datos.
+2. Grafos dirigidos acíclicos y marcos causales.
+3. Diseño de experimentos y pruebas A/B a escala organizacional.
+4. Métodos cuasi-experimentales: variables instrumentales, diferencias en diferencias y pareamiento por puntaje de propensión.
+5. Modelado analítico orientado al soporte de decisiones estratégicas. [Stack: Python, SQL, DoWhy, CausalML, Statsmodels]</t>
         </is>
       </c>
       <c r="F42" s="2" t="n"/>
@@ -1224,11 +1222,11 @@
       </c>
       <c r="E45" s="10" t="inlineStr">
         <is>
-          <t>1. Sesgo algorítmico, equidad informática (Algorithmic Fairness) y discriminación por IA.
-2. Métodos de interpretación y explicación de modelos complejos de caja negra (SHAP, LIME).
-3. Cumplimiento normativo e internacional de privacidad de datos (GDPR, Ley de Inteligencia Artificial de la UE y normativas locales del MEN).
-4. Gobierno de datos y aseguramiento de la robustez frente a ataques adversarios de modelos.
-5. Marcos de auditoría ética y responsabilidad corporativa algorítmica. [Stack: SHAP, LIME, Fairlearn, Alibi, InterpretML]</t>
+          <t>1. Identificación y mitigación de sesgos en modelos de aprendizaje automático.
+2. Térmicas de explicabilidad de caja negra: SHAP y LIME.
+3. Principios de gobernanza de datos y cumplimiento ético-normativo.
+4. Auditoría algorítmica y gestión del riesgo en la adopción de soluciones de IA.
+5. Arquitectura de procesos de datos transparentes e integrados con pipelines corporativos. [Stack: Python, SHAP, LIME, Fairlearn, InterpretML]</t>
         </is>
       </c>
       <c r="F45" s="2" t="n"/>
@@ -1300,7 +1298,7 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Científico de Datos Senior con Doctorado en Ciencias de la Computación / Deep Learning</t>
+          <t>Experto en Aprendizaje Profundo y Ciencias de la Computación</t>
         </is>
       </c>
       <c r="D51" s="2" t="n"/>
@@ -1311,7 +1309,7 @@
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>Ph.D. en Computación o IA con amplias publicaciones científicas indexadas Q1 o Q2 en aprendizaje automático, con amplia experiencia de modelado complejo con frameworks de cómputo en la nube a gran escala.</t>
+          <t>Doctor o Magíster en Ciencias de la Computación, IA o afines, con experiencia acreditada en desarrollo e implementación de modelos de redes neuronales profundas con Python, PyTorch y TensorFlow en entornos productivos.</t>
         </is>
       </c>
       <c r="G51" s="2" t="n"/>
@@ -1330,7 +1328,7 @@
       <c r="B53" s="17" t="inlineStr"/>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Especialista en Inferencia Causal y Econometría Analítica</t>
+          <t>Especialista en Modelamiento Cuantitativo e Inferencia Causal</t>
         </is>
       </c>
       <c r="D53" s="2" t="n"/>
@@ -1341,7 +1339,7 @@
       </c>
       <c r="F53" s="19" t="inlineStr">
         <is>
-          <t>Doctor en Economía Cuantitativa o Estadística Aplicada, con vasta trayectoria laboral en diseño de experimentos de alta precisión de comportamiento de consumo e inferencia para industrias digitales de primer nivel.</t>
+          <t>Doctor o Magíster en Estadística, Economía Cuantitativa o Ciencia de Datos, con trayectoria en diseño experimental, econometría aplicada e inferencia causal para soporte decisional.</t>
         </is>
       </c>
       <c r="G53" s="2" t="n"/>
@@ -1360,7 +1358,7 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Experto en Regulación de Datos y XAI (Explainable AI)</t>
+          <t>Experto en Gobernanza de Datos y Explicabilidad Algorítmica (XAI)</t>
         </is>
       </c>
       <c r="D55" s="2" t="n"/>
@@ -1371,7 +1369,7 @@
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>Ph.D. o Magíster en Ética Aplicada, Derecho de TI o Ciencia de Datos, que haya liderado procesos de auditoría del comportamiento ético de algoritmos de decisión de otorgamiento de crédito o contratación en entidades de la Unión Europea o América Latina.</t>
+          <t>Magíster o Doctor en Ciencia de Datos, Sistemas de Información o Derecho Digital / Ética Tecnológica, con experiencia en auditoría algorítmica, implementación de SHAP/LIME y normativas de datos.</t>
         </is>
       </c>
       <c r="G55" s="2" t="n"/>
@@ -1386,6 +1384,7 @@
       <c r="G56" s="2" t="n"/>
       <c r="H56" s="2" t="n"/>
     </row>
+    <row r="57"/>
     <row r="58" ht="24" customHeight="1">
       <c r="A58" s="11" t="inlineStr">
         <is>
@@ -1409,7 +1408,7 @@
       <c r="B59" s="2" t="n"/>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>PENDIENTE_REVISION (Versión v1)</t>
+          <t>PENDIENTE_REVISION (Versión v2)</t>
         </is>
       </c>
       <c r="D59" s="2" t="n"/>
@@ -1445,7 +1444,7 @@
       <c r="B61" s="2" t="n"/>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>En proceso de revisión</t>
+          <t>2026-10-28 01:43:44</t>
         </is>
       </c>
       <c r="D61" s="2" t="n"/>

--- a/data/curriculo_unicafam/mig_propuestas/PROP_04_Maestr_a_en_Inteligencia__MIG.xlsx
+++ b/data/curriculo_unicafam/mig_propuestas/PROP_04_Maestr_a_en_Inteligencia__MIG.xlsx
@@ -567,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -614,7 +614,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>2.0 (PENDIENTE_REVISION)</t>
+          <t>3.0 (PENDIENTE_REVISION)</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
@@ -631,7 +631,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H3" s="2" t="n"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Según datos del Observatorio de Empleo UniCafam (corte del 2026-10-28, n = 570 ofertas), el rol de Científico de Datos lidera la demanda en el mercado de analítica avanzada con el 31.2% de las ofertas (178 ofertas), seguido por el rol de Machine Learning / AI Engineer con el 18.2% (104 ofertas). A nivel de habilidades requeridas, Python está presente en el 56.7% de las ofertas (323 ofertas), SQL en el 62.3% (355 ofertas), ETL / Pipelines de Datos en el 45.4% (259 ofertas) y Machine Learning General en el 27.5% (157 ofertas). Habilidades especializadas como Deep Learning (4.0%, 23 ofertas), PyTorch (4.2%, 24 ofertas) y TensorFlow / Keras (4.4%, 25 ofertas) complementan las arquitecturas complejas requeridas por las organizaciones. Esta maestría aplicada aborda las brechas técnicas de alto nivel alineando el desarrollo analítico con las exigencias directivas e infraestructurales del mercado local e internacional.</t>
+          <t>Según datos del Observatorio de Empleo UniCafam (corte del 2026-10-28, n = 570 ofertas), el mercado de datos y analítica avanzada está liderado por tres roles principales: Científico de Datos (Data Scientist) con el 31.2% de las ofertas (178 ofertas), Ingeniero de Datos (Data Engineer) con el 25.6% (146 ofertas) y Machine Learning / AI Engineer con el 18.2% (104 ofertas). En cuanto a la demanda general de habilidades (corte 2026-10-28, n = 570), SQL encabeza los requerimientos con el 62.3% (355 ofertas), seguido por Python con el 56.7% (323 ofertas), ETL / Pipelines de Datos con el 45.4% (259 ofertas), Power BI con el 32.1% (183 ofertas), Estadística / Modelamiento con el 30.9% (176 ofertas), Machine Learning General con el 27.5% (157 ofertas), Azure con el 24.0% (137 ofertas), AWS con el 23.5% (134 ofertas), Google Cloud (GCP) con el 19.1% (109 ofertas), Spark / PySpark con el 18.6% (106 ofertas) y Databricks con el 16.8% (96 ofertas). Asimismo, se demandan habilidades especializadas como Airflow (9.3%, 53 ofertas), MLOps (7.4%, 42 ofertas), NLP / LLMs (6.1%, 35 ofertas), Scikit-Learn (6.1%, 35 ofertas), Docker / Kubernetes (5.1%, 29 ofertas), TensorFlow / Keras (4.4%, 25 ofertas), PyTorch (4.2%, 24 ofertas) y Deep Learning (4.0%, 23 ofertas). Esta maestría aplicada de 48 créditos articula de forma integral los perfiles de Científico de Datos, Ingeniero de Datos y Machine Learning / AI Engineer para responder con rigor técnico a las necesidades reales de las organizaciones.</t>
         </is>
       </c>
       <c r="D18" s="2" t="n"/>
@@ -898,10 +898,10 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>• Objetivo General: Formar magísteres con competencias de liderazgo técnico para diseñar, implementar y gestionar soluciones integrales de Inteligencia Artificial y Aprendizaje Automático orientadas a generar valor estratégico en las organizaciones.
-• Objetivo Específico 1: Diseñar arquitecturas de aprendizaje profundo utilizando Python, PyTorch y frameworks avanzados para el procesamiento de datos estructurados y no estructurados.
-• Objetivo Específico 2: Estructurar estrategias de modelamiento decisional y analítica avanzada integrando metodologías de datos para resolver problemas complejos de negocio.
-• Objetivo Específico 3: Implementar esquemas de gobernanza de datos y principios de IA explicable (XAI) asegurando el cumplimiento normativo, la transparencia y la equidad algorítmica.</t>
+          <t>• Objetivo General: Formar magísteres con competencias de liderazgo técnico para diseñar, implementar y gestionar soluciones integrales de Ciencia de Datos, Ingeniería de Datos e Inteligencia Artificial orientadas a generar valor estratégico en las organizaciones.
+• Objetivo Específico 1: Diseñar arquitecturas de ingeniería de datos, pipelines ETL y procesamiento distribuido en la nube (Azure, AWS, GCP, Spark y Databricks) para soportar flujos analíticos escalables.
+• Objetivo Específico 2: Desarrollar modelos avanzados de estadística, aprendizaje automático (Machine Learning) y aprendizaje profundo (Deep Learning, NLP/LLMs) utilizando Python, SQL y frameworks especializados para la toma de decisiones.
+• Objetivo Específico 3: Implementar esquemas de MLOps, visualización estratégica (Power BI) y gobernanza de datos que aseguren el despliegue reproducible, transparente y ético de soluciones de inteligencia artificial.</t>
         </is>
       </c>
       <c r="D22" s="2" t="n"/>
@@ -980,7 +980,7 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Seminarios aplicados integrados con laboratorios computacionales prácticos. El programa se centra en el desarrollo de un Proyecto de Grado de Aplicación Industrial orientado a resolver problemas analíticos reales de alto impacto técnico y organizacional.</t>
+          <t>Seminarios aplicados integrados con laboratorios computacionales prácticos. El programa se estructura en 8 módulos (48 créditos en total) centrados en la resolución de problemas reales y culmina con el desarrollo de un Proyecto de Grado de Aplicación Industrial de alto impacto técnico y organizacional.</t>
         </is>
       </c>
       <c r="D29" s="2" t="n"/>
@@ -1024,8 +1024,8 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>✔ Formación rigurosa alineada con las habilidades de mayor demanda del mercado: Python (56.7% de ofertas) y SQL (62.3% de ofertas) según corte 2026-10-28 (n = 570).
-✔ Integración de pipelines de datos (ETL) y marcos de gobernanza algorítmica aplicados a la toma de decisiones empresariales.
+          <t>✔ Formación rigurosa alineada con las habilidades de mayor demanda del mercado según el Observatorio de Empleo UniCafam (corte 2026-10-28, n = 570): SQL (62.3%, 355 ofertas), Python (56.7%, 323 ofertas), ETL / Pipelines de Datos (45.4%, 259 ofertas) y Power BI (32.1%, 183 ofertas).
+✔ Cobertura integral de los tres roles más demandados del sector (corte 2026-10-28, n = 570): Científico de Datos (31.2%, 178 ofertas), Ingeniero de Datos (25.6%, 146 ofertas) y Machine Learning / AI Engineer (18.2%, 104 ofertas).
 ✔ Posibilidad de articulación y homologación de créditos para egresados de posgrados de la Escuela de Ingeniería de UniCafam conforme a normativa institucional.</t>
         </is>
       </c>
@@ -1119,27 +1119,27 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Modelado Avanzado de Aprendizaje Profundo &amp; Redes Neuronales</t>
+          <t>Programación Avanzada en Python y Gestión de Datos con SQL</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>1. Fundamentos de aprendizaje profundo y retropropagación.
-2. Arquitecturas convolucionales para visión por computador.
-3. Redes recurrentes y procesamiento de secuencias temporales.
-4. Mecanismos de atención y arquitecturas basadas en Transformers.
-5. Ajuste fino de modelos y optimización de cómputo en PyTorch y TensorFlow. [Stack: Python, PyTorch, TensorFlow, Keras, Hugging Face]</t>
+          <t>1. Estructuras de datos avanzadas, programación orientada a objetos y funcional en Python para ciencia de datos.
+2. Optimización de consultas SQL, funciones de ventana, particionamiento y diseño de bases de datos relacionales.
+3. Integración de bases de datos NoSQL y manejo de datos semiestructurados.
+4. Control de versiones con Git y buenas prácticas de ingeniería de software para datos.
+5. Procesamiento eficiente en memoria y vectorización numérica. [Stack: Python, SQL, Git / Control de Versiones, Bases de Datos NoSQL]</t>
         </is>
       </c>
       <c r="F39" s="2" t="n"/>
       <c r="G39" s="15" t="inlineStr">
         <is>
-          <t>Semanas 1 a 12 (Primer Semestre)</t>
+          <t>Semanas 1 a 8 (Primer Semestre)</t>
         </is>
       </c>
       <c r="H39" s="16" t="inlineStr">
         <is>
-          <t>192 h</t>
+          <t>288 h</t>
         </is>
       </c>
     </row>
@@ -1168,27 +1168,27 @@
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>Inferencia Causal &amp; Modelamiento Decisional para Negocios</t>
+          <t>Inferencia Estadística, Modelamiento Matemático y Experimentación</t>
         </is>
       </c>
       <c r="E42" s="19" t="inlineStr">
         <is>
-          <t>1. Principios de causalidad vs. correlación en ciencia de datos.
-2. Grafos dirigidos acíclicos y marcos causales.
-3. Diseño de experimentos y pruebas A/B a escala organizacional.
-4. Métodos cuasi-experimentales: variables instrumentales, diferencias en diferencias y pareamiento por puntaje de propensión.
-5. Modelado analítico orientado al soporte de decisiones estratégicas. [Stack: Python, SQL, DoWhy, CausalML, Statsmodels]</t>
+          <t>1. Fundamentos de probabilidad, inferencia estadística paramétrica y no paramétrica.
+2. Modelamiento lineal generalizado, análisis multivariado y reducción de dimensionalidad.
+3. Diseño de experimentos, pruebas de hipótesis e inferencia causal para decisiones de negocio.
+4. Análisis de series de tiempo y pronósticos econométricos.
+5. Programación estadística combinada en Python y R para validación de supuestos. [Stack: Python, R, SQL, Scikit-Learn]</t>
         </is>
       </c>
       <c r="F42" s="2" t="n"/>
       <c r="G42" s="20" t="inlineStr">
         <is>
-          <t>Semanas 1 a 12 (Segundo Semestre)</t>
+          <t>Semanas 9 a 16 (Primer Semestre)</t>
         </is>
       </c>
       <c r="H42" s="21" t="inlineStr">
         <is>
-          <t>192 h</t>
+          <t>288 h</t>
         </is>
       </c>
     </row>
@@ -1217,27 +1217,27 @@
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Gobernanza de Datos, Ética en IA &amp; Algoritmos Explicables (XAI)</t>
+          <t>Ingeniería de Datos, Arquitecturas ETL y Orquestación de Pipelines</t>
         </is>
       </c>
       <c r="E45" s="10" t="inlineStr">
         <is>
-          <t>1. Identificación y mitigación de sesgos en modelos de aprendizaje automático.
-2. Térmicas de explicabilidad de caja negra: SHAP y LIME.
-3. Principios de gobernanza de datos y cumplimiento ético-normativo.
-4. Auditoría algorítmica y gestión del riesgo en la adopción de soluciones de IA.
-5. Arquitectura de procesos de datos transparentes e integrados con pipelines corporativos. [Stack: Python, SHAP, LIME, Fairlearn, InterpretML]</t>
+          <t>1. Diseño de arquitecturas de datos modernas: Data Warehouses, Data Lakes y Data Lakehouses.
+2. Construcción de procesos de extracción, transformación y carga (ETL / ELT) robustos y escalables.
+3. Orquestación y automatización de flujos de trabajo de datos mediante Apache Airflow.
+4. Ingesta de datos en tiempo real y arquitecturas orientadas a eventos con Apache Kafka.
+5. Calidad de datos, trazabilidad y pruebas automatizadas en pipelines. [Stack: ETL / Pipelines de Datos, SQL, Python, Airflow, Kafka]</t>
         </is>
       </c>
       <c r="F45" s="2" t="n"/>
       <c r="G45" s="15" t="inlineStr">
         <is>
-          <t>Semanas 1 a 12 (Tercer Semestre)</t>
+          <t>Semanas 1 a 8 (Segundo Semestre)</t>
         </is>
       </c>
       <c r="H45" s="16" t="inlineStr">
         <is>
-          <t>192 h</t>
+          <t>288 h</t>
         </is>
       </c>
     </row>
@@ -1259,63 +1259,87 @@
       <c r="G47" s="2" t="n"/>
       <c r="H47" s="2" t="n"/>
     </row>
-    <row r="48" ht="10" customHeight="1"/>
-    <row r="49" ht="20" customHeight="1">
-      <c r="B49" s="11" t="inlineStr">
-        <is>
-          <t>DOCENTES</t>
-        </is>
-      </c>
-      <c r="C49" s="12" t="inlineStr">
-        <is>
-          <t>Nombre del Docente / Rol</t>
-        </is>
-      </c>
-      <c r="D49" s="13" t="n"/>
-      <c r="E49" s="12" t="inlineStr">
-        <is>
-          <t>Módulo Asignado</t>
-        </is>
-      </c>
-      <c r="F49" s="12" t="inlineStr">
-        <is>
-          <t>Perfil de Experto / Requisitos y Credenciales</t>
-        </is>
-      </c>
-      <c r="G49" s="13" t="n"/>
-      <c r="H49" s="13" t="n"/>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="B50" s="13" t="n"/>
-      <c r="C50" s="13" t="n"/>
-      <c r="D50" s="13" t="n"/>
-      <c r="E50" s="13" t="n"/>
-      <c r="F50" s="13" t="n"/>
-      <c r="G50" s="13" t="n"/>
-      <c r="H50" s="13" t="n"/>
-    </row>
-    <row r="51" ht="24" customHeight="1">
+    <row r="48" ht="22" customHeight="1">
+      <c r="B48" s="17" t="inlineStr"/>
+      <c r="C48" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>Ecosistemas Cloud, Big Data y Procesamiento Distribuido</t>
+        </is>
+      </c>
+      <c r="E48" s="19" t="inlineStr">
+        <is>
+          <t>1. Arquitecturas y servicios de datos en la nube: Microsoft Azure, Amazon Web Services (AWS) y Google Cloud (GCP).
+2. Procesamiento distribuido de grandes volúmenes de datos con Apache Spark y PySpark.
+3. Analítica unificada e ingeniería colaborativa sobre la plataforma Databricks.
+4. Gestión de clústeres, almacenamiento distribuido (Hadoop / Hive) y programación funcional en Scala.
+5. Optimización de costos y rendimiento computacional en infraestructuras cloud. [Stack: Azure, AWS, Google Cloud (GCP), Spark / PySpark, Databricks, Hadoop / Hive, Scala]</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="n"/>
+      <c r="G48" s="20" t="inlineStr">
+        <is>
+          <t>Semanas 9 a 16 (Segundo Semestre)</t>
+        </is>
+      </c>
+      <c r="H48" s="21" t="inlineStr">
+        <is>
+          <t>288 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="B49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n"/>
+      <c r="E49" s="2" t="n"/>
+      <c r="F49" s="2" t="n"/>
+      <c r="G49" s="2" t="n"/>
+      <c r="H49" s="2" t="n"/>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n"/>
+      <c r="E50" s="2" t="n"/>
+      <c r="F50" s="2" t="n"/>
+      <c r="G50" s="2" t="n"/>
+      <c r="H50" s="2" t="n"/>
+    </row>
+    <row r="51" ht="22" customHeight="1">
       <c r="B51" s="2" t="inlineStr"/>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>Experto en Aprendizaje Profundo y Ciencias de la Computación</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="n"/>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>Modelado Avanzado de Aprendizaje Profundo &amp; Redes Neuronales</t>
-        </is>
-      </c>
-      <c r="F51" s="10" t="inlineStr">
-        <is>
-          <t>Doctor o Magíster en Ciencias de la Computación, IA o afines, con experiencia acreditada en desarrollo e implementación de modelos de redes neuronales profundas con Python, PyTorch y TensorFlow en entornos productivos.</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="n"/>
-      <c r="H51" s="2" t="n"/>
-    </row>
-    <row r="52" ht="24" customHeight="1">
+      <c r="C51" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>Aprendizaje Automático (Machine Learning) Aplicado a Negocios</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>1. Algoritmos de aprendizaje supervisado: regresión regularizada, máquinas de soporte vectorial y árboles de decisión.
+2. Métodos de ensamble avanzados (Random Forest, Gradient Boosting, XGBoost, LightGBM).
+3. Aprendizaje no supervisado: clustering, detección de anomalías y sistemas de recomendación.
+4. Ingeniería de características (Feature Engineering), validación cruzada y ajuste de hiperparámetros con Scikit-Learn.
+5. Evaluación de modelos mediante métricas técnicas y de impacto financiero. [Stack: Python, Machine Learning General, Scikit-Learn, SQL]</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="n"/>
+      <c r="G51" s="15" t="inlineStr">
+        <is>
+          <t>Semanas 1 a 8 (Tercer Semestre)</t>
+        </is>
+      </c>
+      <c r="H51" s="16" t="inlineStr">
+        <is>
+          <t>288 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
       <c r="B52" s="2" t="n"/>
       <c r="C52" s="2" t="n"/>
       <c r="D52" s="2" t="n"/>
@@ -1324,58 +1348,56 @@
       <c r="G52" s="2" t="n"/>
       <c r="H52" s="2" t="n"/>
     </row>
-    <row r="53" ht="24" customHeight="1">
-      <c r="B53" s="17" t="inlineStr"/>
-      <c r="C53" s="9" t="inlineStr">
-        <is>
-          <t>Especialista en Modelamiento Cuantitativo e Inferencia Causal</t>
-        </is>
-      </c>
+    <row r="53" ht="22" customHeight="1">
+      <c r="B53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="n"/>
-      <c r="E53" s="22" t="inlineStr">
-        <is>
-          <t>Inferencia Causal &amp; Modelamiento Decisional para Negocios</t>
-        </is>
-      </c>
-      <c r="F53" s="19" t="inlineStr">
-        <is>
-          <t>Doctor o Magíster en Estadística, Economía Cuantitativa o Ciencia de Datos, con trayectoria en diseño experimental, econometría aplicada e inferencia causal para soporte decisional.</t>
-        </is>
-      </c>
+      <c r="E53" s="2" t="n"/>
+      <c r="F53" s="2" t="n"/>
       <c r="G53" s="2" t="n"/>
       <c r="H53" s="2" t="n"/>
     </row>
-    <row r="54" ht="24" customHeight="1">
-      <c r="B54" s="2" t="n"/>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n"/>
-      <c r="E54" s="2" t="n"/>
+    <row r="54" ht="22" customHeight="1">
+      <c r="B54" s="17" t="inlineStr"/>
+      <c r="C54" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>Aprendizaje Profundo (Deep Learning), NLP y Modelos de Lenguaje (LLMs)</t>
+        </is>
+      </c>
+      <c r="E54" s="19" t="inlineStr">
+        <is>
+          <t>1. Fundamentos de redes neuronales profundas, retropropagación y optimización en PyTorch y TensorFlow / Keras.
+2. Procesamiento de Lenguaje Natural (NLP), embeddings y arquitecturas basadas en Transformers.
+3. Grandes Modelos de Lenguaje (LLMs), ajuste fino (Fine-Tuning) y Generación Aumentada por Recuperación (RAG).
+4. Arquitecturas convolucionales aplicadas a visión por computador (Computer Vision) y datos no estructurados.
+5. Evaluación de rendimiento computacional y mitigación de alucinaciones en IA generativa. [Stack: Python, NLP / LLMs, TensorFlow / Keras, PyTorch, Deep Learning, Computer Vision]</t>
+        </is>
+      </c>
       <c r="F54" s="2" t="n"/>
-      <c r="G54" s="2" t="n"/>
-      <c r="H54" s="2" t="n"/>
-    </row>
-    <row r="55" ht="24" customHeight="1">
-      <c r="B55" s="2" t="inlineStr"/>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>Experto en Gobernanza de Datos y Explicabilidad Algorítmica (XAI)</t>
-        </is>
-      </c>
+      <c r="G54" s="20" t="inlineStr">
+        <is>
+          <t>Semanas 9 a 16 (Tercer Semestre)</t>
+        </is>
+      </c>
+      <c r="H54" s="21" t="inlineStr">
+        <is>
+          <t>288 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="B55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
       <c r="D55" s="2" t="n"/>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>Gobernanza de Datos, Ética en IA &amp; Algoritmos Explicables (XAI)</t>
-        </is>
-      </c>
-      <c r="F55" s="10" t="inlineStr">
-        <is>
-          <t>Magíster o Doctor en Ciencia de Datos, Sistemas de Información o Derecho Digital / Ética Tecnológica, con experiencia en auditoría algorítmica, implementación de SHAP/LIME y normativas de datos.</t>
-        </is>
-      </c>
+      <c r="E55" s="2" t="n"/>
+      <c r="F55" s="2" t="n"/>
       <c r="G55" s="2" t="n"/>
       <c r="H55" s="2" t="n"/>
     </row>
-    <row r="56" ht="24" customHeight="1">
+    <row r="56" ht="22" customHeight="1">
       <c r="B56" s="2" t="n"/>
       <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="n"/>
@@ -1384,149 +1406,572 @@
       <c r="G56" s="2" t="n"/>
       <c r="H56" s="2" t="n"/>
     </row>
-    <row r="57"/>
-    <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="11" t="inlineStr">
-        <is>
-          <t>GOBERNANZA CURRICULAR Y TRAZABILIDAD DE APROBACIÓN (MEN DECRETO 1330)</t>
-        </is>
-      </c>
-      <c r="B58" s="13" t="n"/>
-      <c r="C58" s="13" t="n"/>
-      <c r="D58" s="13" t="n"/>
-      <c r="E58" s="13" t="n"/>
-      <c r="F58" s="13" t="n"/>
-      <c r="G58" s="13" t="n"/>
-      <c r="H58" s="13" t="n"/>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="23" t="inlineStr">
-        <is>
-          <t>ESTADO DE APROBACIÓN</t>
-        </is>
-      </c>
+    <row r="57" ht="22" customHeight="1">
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>MLOps, Despliegue en Producción y Gobernanza de IA</t>
+        </is>
+      </c>
+      <c r="E57" s="10" t="inlineStr">
+        <is>
+          <t>1. Principios de MLOps: integración continua, entrega continua y entrenamiento continuo (CI/CD/CT) de modelos.
+2. Contenerización y orquestación de microservicios analíticos con Docker y Kubernetes.
+3. Monitoreo de modelos en producción, detección de Data Drift y Model Drift en Azure y AWS.
+4. Gobernanza de datos, ética algorítmica, explicabilidad (XAI) y cumplimiento normativo.
+5. Integración de alto rendimiento y despliegue en entornos empresariales. [Stack: MLOps, Docker / Kubernetes, Git / Control de Versiones, Python, Azure, AWS]</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="n"/>
+      <c r="G57" s="15" t="inlineStr">
+        <is>
+          <t>Semanas 1 a 8 (Cuarto Semestre)</t>
+        </is>
+      </c>
+      <c r="H57" s="16" t="inlineStr">
+        <is>
+          <t>288 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="B58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n"/>
+      <c r="E58" s="2" t="n"/>
+      <c r="F58" s="2" t="n"/>
+      <c r="G58" s="2" t="n"/>
+      <c r="H58" s="2" t="n"/>
+    </row>
+    <row r="59" ht="22" customHeight="1">
       <c r="B59" s="2" t="n"/>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>PENDIENTE_REVISION (Versión v2)</t>
-        </is>
-      </c>
+      <c r="C59" s="2" t="n"/>
       <c r="D59" s="2" t="n"/>
       <c r="E59" s="2" t="n"/>
       <c r="F59" s="2" t="n"/>
       <c r="G59" s="2" t="n"/>
       <c r="H59" s="2" t="n"/>
     </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="23" t="inlineStr">
-        <is>
-          <t>AVAL / DECISIÓN DIRECTIVA</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="n"/>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente de Visto Bueno por Comité Curricular</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="n"/>
-      <c r="E60" s="2" t="n"/>
+    <row r="60" ht="22" customHeight="1">
+      <c r="B60" s="17" t="inlineStr"/>
+      <c r="C60" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>Visualización Ejecutiva, Analítica Estratégica y Proyecto Aplicado de Grado</t>
+        </is>
+      </c>
+      <c r="E60" s="19" t="inlineStr">
+        <is>
+          <t>1. Diseño de tableros ejecutivos e inteligencia de negocios avanzada con Power BI, Tableau y Looker.
+2. Storytelling con datos y traducción de modelos analíticos complejos en indicadores clave de negocio (KPIs).
+3. Estructuración, ejecución y validación técnica del Proyecto de Grado de Aplicación Industrial.
+4. Integración de extremo a extremo: desde la ingesta (ETL/SQL) y el modelamiento (Python/ML) hasta la visualización directiva.
+5. Sustentación de resultados e impacto estratégico ante comités directivos. [Stack: Power BI, Tableau, Looker, SQL, Python, Excel Avanzado]</t>
+        </is>
+      </c>
       <c r="F60" s="2" t="n"/>
-      <c r="G60" s="2" t="n"/>
-      <c r="H60" s="2" t="n"/>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="23" t="inlineStr">
-        <is>
-          <t>FECHA ÚLTIMA DECISIÓN</t>
-        </is>
-      </c>
+      <c r="G60" s="20" t="inlineStr">
+        <is>
+          <t>Semanas 9 a 16 (Cuarto Semestre)</t>
+        </is>
+      </c>
+      <c r="H60" s="21" t="inlineStr">
+        <is>
+          <t>288 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
       <c r="B61" s="2" t="n"/>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-28 01:43:44</t>
-        </is>
-      </c>
+      <c r="C61" s="2" t="n"/>
       <c r="D61" s="2" t="n"/>
       <c r="E61" s="2" t="n"/>
       <c r="F61" s="2" t="n"/>
       <c r="G61" s="2" t="n"/>
       <c r="H61" s="2" t="n"/>
     </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="B62" s="2" t="n"/>
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="2" t="n"/>
+      <c r="E62" s="2" t="n"/>
+      <c r="F62" s="2" t="n"/>
+      <c r="G62" s="2" t="n"/>
+      <c r="H62" s="2" t="n"/>
+    </row>
+    <row r="63" ht="10" customHeight="1"/>
+    <row r="64" ht="20" customHeight="1">
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>DOCENTES</t>
+        </is>
+      </c>
+      <c r="C64" s="12" t="inlineStr">
+        <is>
+          <t>Nombre del Docente / Rol</t>
+        </is>
+      </c>
+      <c r="D64" s="13" t="n"/>
+      <c r="E64" s="12" t="inlineStr">
+        <is>
+          <t>Módulo Asignado</t>
+        </is>
+      </c>
+      <c r="F64" s="12" t="inlineStr">
+        <is>
+          <t>Perfil de Experto / Requisitos y Credenciales</t>
+        </is>
+      </c>
+      <c r="G64" s="13" t="n"/>
+      <c r="H64" s="13" t="n"/>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="B65" s="13" t="n"/>
+      <c r="C65" s="13" t="n"/>
+      <c r="D65" s="13" t="n"/>
+      <c r="E65" s="13" t="n"/>
+      <c r="F65" s="13" t="n"/>
+      <c r="G65" s="13" t="n"/>
+      <c r="H65" s="13" t="n"/>
+    </row>
+    <row r="66" ht="24" customHeight="1">
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>Especialista en Ingeniería de Software para Datos y Bases de Datos</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n"/>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>Programación Avanzada en Python y Gestión de Datos con SQL</t>
+        </is>
+      </c>
+      <c r="F66" s="10" t="inlineStr">
+        <is>
+          <t>Magíster o Doctor en Ingeniería de Sistemas o Ciencias de la Computación, con experiencia superior a 5 años en desarrollo avanzado con Python, optimización de bases de datos SQL/NoSQL y control de versiones con Git.</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="n"/>
+      <c r="H66" s="2" t="n"/>
+    </row>
+    <row r="67" ht="24" customHeight="1">
+      <c r="B67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n"/>
+      <c r="E67" s="2" t="n"/>
+      <c r="F67" s="2" t="n"/>
+      <c r="G67" s="2" t="n"/>
+      <c r="H67" s="2" t="n"/>
+    </row>
+    <row r="68" ht="24" customHeight="1">
+      <c r="B68" s="17" t="inlineStr"/>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>Especialista en Modelamiento Cuantitativo e Inferencia Estadística</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n"/>
+      <c r="E68" s="22" t="inlineStr">
+        <is>
+          <t>Inferencia Estadística, Modelamiento Matemático y Experimentación</t>
+        </is>
+      </c>
+      <c r="F68" s="19" t="inlineStr">
+        <is>
+          <t>Doctor o Magíster en Estadística, Matemáticas Aplicadas o Ciencia de Datos, con trayectoria acreditada en diseño experimental, modelamiento estadístico y programación analítica en Python y R.</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="n"/>
+      <c r="H68" s="2" t="n"/>
+    </row>
+    <row r="69" ht="24" customHeight="1">
+      <c r="B69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="n"/>
+      <c r="E69" s="2" t="n"/>
+      <c r="F69" s="2" t="n"/>
+      <c r="G69" s="2" t="n"/>
+      <c r="H69" s="2" t="n"/>
+    </row>
+    <row r="70" ht="24" customHeight="1">
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>Arquitecto de Ingeniería de Datos y Orquestación de Pipelines</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n"/>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>Ingeniería de Datos, Arquitecturas ETL y Orquestación de Pipelines</t>
+        </is>
+      </c>
+      <c r="F70" s="10" t="inlineStr">
+        <is>
+          <t>Magíster en Ingeniería de Datos, Sistemas o afines, con experiencia comprobada en diseño de Data Warehouses, construcción de pipelines ETL/ELT a escala industrial y orquestación con Apache Airflow y Kafka.</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="n"/>
+      <c r="H70" s="2" t="n"/>
+    </row>
+    <row r="71" ht="24" customHeight="1">
+      <c r="B71" s="2" t="n"/>
+      <c r="C71" s="2" t="n"/>
+      <c r="D71" s="2" t="n"/>
+      <c r="E71" s="2" t="n"/>
+      <c r="F71" s="2" t="n"/>
+      <c r="G71" s="2" t="n"/>
+      <c r="H71" s="2" t="n"/>
+    </row>
+    <row r="72" ht="24" customHeight="1">
+      <c r="B72" s="17" t="inlineStr"/>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>Arquitecto Cloud y Especialista en Big Data</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n"/>
+      <c r="E72" s="22" t="inlineStr">
+        <is>
+          <t>Ecosistemas Cloud, Big Data y Procesamiento Distribuido</t>
+        </is>
+      </c>
+      <c r="F72" s="19" t="inlineStr">
+        <is>
+          <t>Magíster en Ingeniería o Ciencias de la Computación, certificado en arquitecturas cloud (Azure, AWS o GCP) y con experiencia práctica liderando proyectos de procesamiento distribuido con Spark / PySpark y Databricks.</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="n"/>
+      <c r="H72" s="2" t="n"/>
+    </row>
+    <row r="73" ht="24" customHeight="1">
+      <c r="B73" s="2" t="n"/>
+      <c r="C73" s="2" t="n"/>
+      <c r="D73" s="2" t="n"/>
+      <c r="E73" s="2" t="n"/>
+      <c r="F73" s="2" t="n"/>
+      <c r="G73" s="2" t="n"/>
+      <c r="H73" s="2" t="n"/>
+    </row>
+    <row r="74" ht="24" customHeight="1">
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>Científico de Datos Senior en Aprendizaje Automático</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n"/>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>Aprendizaje Automático (Machine Learning) Aplicado a Negocios</t>
+        </is>
+      </c>
+      <c r="F74" s="10" t="inlineStr">
+        <is>
+          <t>Doctor o Magíster en Ciencia de Datos, Inteligencia Artificial o Estadística, con amplia trayectoria en el diseño, validación y puesta en valor de modelos supervisados y no supervisados con Python y Scikit-Learn.</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="n"/>
+      <c r="H74" s="2" t="n"/>
+    </row>
+    <row r="75" ht="24" customHeight="1">
+      <c r="B75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="n"/>
+      <c r="E75" s="2" t="n"/>
+      <c r="F75" s="2" t="n"/>
+      <c r="G75" s="2" t="n"/>
+      <c r="H75" s="2" t="n"/>
+    </row>
+    <row r="76" ht="24" customHeight="1">
+      <c r="B76" s="17" t="inlineStr"/>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>Experto en Aprendizaje Profundo, NLP e IA Generativa</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n"/>
+      <c r="E76" s="22" t="inlineStr">
+        <is>
+          <t>Aprendizaje Profundo (Deep Learning), NLP y Modelos de Lenguaje (LLMs)</t>
+        </is>
+      </c>
+      <c r="F76" s="19" t="inlineStr">
+        <is>
+          <t>Doctor o Magíster en Ciencias de la Computación o Inteligencia Artificial, con experiencia acreditada en implementación de redes neuronales profundas, LLMs y visión por computador utilizando PyTorch y TensorFlow / Keras.</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="n"/>
+      <c r="H76" s="2" t="n"/>
+    </row>
+    <row r="77" ht="24" customHeight="1">
+      <c r="B77" s="2" t="n"/>
+      <c r="C77" s="2" t="n"/>
+      <c r="D77" s="2" t="n"/>
+      <c r="E77" s="2" t="n"/>
+      <c r="F77" s="2" t="n"/>
+      <c r="G77" s="2" t="n"/>
+      <c r="H77" s="2" t="n"/>
+    </row>
+    <row r="78" ht="24" customHeight="1">
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>Ingeniero Principal de MLOps y Gobernanza de IA</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n"/>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>MLOps, Despliegue en Producción y Gobernanza de IA</t>
+        </is>
+      </c>
+      <c r="F78" s="10" t="inlineStr">
+        <is>
+          <t>Magíster en Ingeniería de Software, Ciencia de Datos o Inteligencia Artificial, con experiencia en despliegue de modelos en producción con Docker/Kubernetes, automatización MLOps en Azure/AWS y marcos de gobernanza algorítmica.</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="n"/>
+      <c r="H78" s="2" t="n"/>
+    </row>
+    <row r="79" ht="24" customHeight="1">
+      <c r="B79" s="2" t="n"/>
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="2" t="n"/>
+      <c r="E79" s="2" t="n"/>
+      <c r="F79" s="2" t="n"/>
+      <c r="G79" s="2" t="n"/>
+      <c r="H79" s="2" t="n"/>
+    </row>
+    <row r="80" ht="24" customHeight="1">
+      <c r="B80" s="17" t="inlineStr"/>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>Director de Analítica Estratégica e Inteligencia de Negocios</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n"/>
+      <c r="E80" s="22" t="inlineStr">
+        <is>
+          <t>Visualización Ejecutiva, Analítica Estratégica y Proyecto Aplicado de Grado</t>
+        </is>
+      </c>
+      <c r="F80" s="19" t="inlineStr">
+        <is>
+          <t>Magíster o Doctor en Ciencia de Datos, Ingeniería Industrial o Administración de Negocios, con experiencia directiva en estrategia de datos, visualización ejecutiva con Power BI/Tableau y dirección de proyectos aplicados de analítica.</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="n"/>
+      <c r="H80" s="2" t="n"/>
+    </row>
+    <row r="81" ht="24" customHeight="1">
+      <c r="B81" s="2" t="n"/>
+      <c r="C81" s="2" t="n"/>
+      <c r="D81" s="2" t="n"/>
+      <c r="E81" s="2" t="n"/>
+      <c r="F81" s="2" t="n"/>
+      <c r="G81" s="2" t="n"/>
+      <c r="H81" s="2" t="n"/>
+    </row>
+    <row r="82"/>
+    <row r="83" ht="24" customHeight="1">
+      <c r="A83" s="11" t="inlineStr">
+        <is>
+          <t>GOBERNANZA CURRICULAR Y TRAZABILIDAD DE APROBACIÓN (MEN DECRETO 1330)</t>
+        </is>
+      </c>
+      <c r="B83" s="13" t="n"/>
+      <c r="C83" s="13" t="n"/>
+      <c r="D83" s="13" t="n"/>
+      <c r="E83" s="13" t="n"/>
+      <c r="F83" s="13" t="n"/>
+      <c r="G83" s="13" t="n"/>
+      <c r="H83" s="13" t="n"/>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="23" t="inlineStr">
+        <is>
+          <t>ESTADO DE APROBACIÓN</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="n"/>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>PENDIENTE_REVISION (Versión v3)</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n"/>
+      <c r="E84" s="2" t="n"/>
+      <c r="F84" s="2" t="n"/>
+      <c r="G84" s="2" t="n"/>
+      <c r="H84" s="2" t="n"/>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="23" t="inlineStr">
+        <is>
+          <t>AVAL / DECISIÓN DIRECTIVA</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="n"/>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente de Visto Bueno por Comité Curricular</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n"/>
+      <c r="E85" s="2" t="n"/>
+      <c r="F85" s="2" t="n"/>
+      <c r="G85" s="2" t="n"/>
+      <c r="H85" s="2" t="n"/>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="23" t="inlineStr">
+        <is>
+          <t>FECHA ÚLTIMA DECISIÓN</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="n"/>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29 01:21:42</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n"/>
+      <c r="E86" s="2" t="n"/>
+      <c r="F86" s="2" t="n"/>
+      <c r="G86" s="2" t="n"/>
+      <c r="H86" s="2" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="72">
-    <mergeCell ref="B22:B25"/>
+  <mergeCells count="122">
+    <mergeCell ref="C85:H85"/>
+    <mergeCell ref="G54:G56"/>
+    <mergeCell ref="A83:H83"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="C51:C53"/>
+    <mergeCell ref="C48:C50"/>
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="E48:F50"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="E74:E75"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="B29:B32"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="H54:H56"/>
+    <mergeCell ref="E76:E77"/>
+    <mergeCell ref="C29:H32"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="C74:D75"/>
+    <mergeCell ref="C68:D69"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="G42:G44"/>
+    <mergeCell ref="C22:H25"/>
+    <mergeCell ref="B57:B59"/>
+    <mergeCell ref="D57:D59"/>
+    <mergeCell ref="H51:H53"/>
+    <mergeCell ref="H60:H62"/>
+    <mergeCell ref="C80:D81"/>
+    <mergeCell ref="H57:H59"/>
+    <mergeCell ref="F64:H65"/>
     <mergeCell ref="C10:H10"/>
     <mergeCell ref="C16:H16"/>
-    <mergeCell ref="C55:D56"/>
     <mergeCell ref="G45:G47"/>
-    <mergeCell ref="C39:C41"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="E51:E52"/>
-    <mergeCell ref="C9:H9"/>
-    <mergeCell ref="B12:B15"/>
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="C26:H28"/>
     <mergeCell ref="E42:F44"/>
-    <mergeCell ref="F49:H50"/>
+    <mergeCell ref="E64:E65"/>
+    <mergeCell ref="E78:E79"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D42:D44"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="C59:H59"/>
-    <mergeCell ref="C51:D52"/>
+    <mergeCell ref="C70:D71"/>
     <mergeCell ref="E39:F41"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="D39:D41"/>
     <mergeCell ref="E38:F38"/>
-    <mergeCell ref="C60:H60"/>
+    <mergeCell ref="F68:H69"/>
+    <mergeCell ref="C78:D79"/>
+    <mergeCell ref="H42:H44"/>
+    <mergeCell ref="B1:E4"/>
+    <mergeCell ref="C54:C56"/>
+    <mergeCell ref="G48:G50"/>
+    <mergeCell ref="G57:G59"/>
+    <mergeCell ref="C64:D65"/>
+    <mergeCell ref="E66:E67"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="E57:F59"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="H45:H47"/>
+    <mergeCell ref="F72:H73"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="E54:F56"/>
+    <mergeCell ref="D48:D50"/>
+    <mergeCell ref="E68:E69"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="C66:D67"/>
+    <mergeCell ref="G60:G62"/>
+    <mergeCell ref="B51:B53"/>
     <mergeCell ref="B26:B28"/>
-    <mergeCell ref="F53:H54"/>
+    <mergeCell ref="C72:D73"/>
+    <mergeCell ref="D51:D53"/>
     <mergeCell ref="C18:H21"/>
+    <mergeCell ref="D60:D62"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="F74:H75"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="E70:E71"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="G39:G41"/>
+    <mergeCell ref="F76:H77"/>
+    <mergeCell ref="E80:E81"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="E45:F47"/>
+    <mergeCell ref="F66:H67"/>
+    <mergeCell ref="C86:H86"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="D45:D47"/>
+    <mergeCell ref="C33:H35"/>
+    <mergeCell ref="H39:H41"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C60:C62"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="C57:C59"/>
+    <mergeCell ref="C84:H84"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="G51:G53"/>
+    <mergeCell ref="C76:D77"/>
+    <mergeCell ref="F78:H79"/>
+    <mergeCell ref="B54:B56"/>
+    <mergeCell ref="D54:D56"/>
+    <mergeCell ref="H48:H50"/>
+    <mergeCell ref="E51:F53"/>
+    <mergeCell ref="E60:F62"/>
     <mergeCell ref="D13:H13"/>
-    <mergeCell ref="C61:H61"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="H42:H44"/>
-    <mergeCell ref="C8:H8"/>
-    <mergeCell ref="C53:D54"/>
-    <mergeCell ref="B29:B32"/>
-    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="F80:H81"/>
+    <mergeCell ref="A84:B84"/>
     <mergeCell ref="C42:C44"/>
     <mergeCell ref="C7:H7"/>
     <mergeCell ref="G3:H3"/>
-    <mergeCell ref="B1:E4"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="F55:H56"/>
-    <mergeCell ref="C29:H32"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="G39:G41"/>
-    <mergeCell ref="G42:G44"/>
-    <mergeCell ref="C22:H25"/>
-    <mergeCell ref="C49:D50"/>
-    <mergeCell ref="F51:H52"/>
-    <mergeCell ref="E45:F47"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="F70:H71"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="B76:B77"/>
     <mergeCell ref="G4:H4"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D45:D47"/>
-    <mergeCell ref="C33:H35"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="H39:H41"/>
-    <mergeCell ref="H45:H47"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="E53:E54"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="B60:B62"/>
     <mergeCell ref="E37:F37"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A58:H58"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
